--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484091_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484091_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.8033</v>
+        <v>-0.7732</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2112</v>
+        <v>-0.4836</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0145</v>
+        <v>-0.2896</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.8183</v>
+        <v>-1.6523</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9052</v>
+        <v>-0.9981</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.7234</v>
+        <v>-0.6542</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7702</v>
+        <v>-0.5391</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5658</v>
+        <v>-0.5391</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7956</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5885</v>
+        <v>-1.1132</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6607</v>
+        <v>-0.459</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.9278</v>
+        <v>-0.6542</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4235</v>
+        <v>-0.2678</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2382</v>
+        <v>-0.4251</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1853</v>
+        <v>0.1572</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1947</v>
+        <v>1.5437</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1947</v>
+        <v>1.4724</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>P. PARISI TRIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8698</v>
+        <v>-1.0745</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6083</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2615</v>
+        <v>-0.9798</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6523</v>
+        <v>-2.8856</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9981</v>
+        <v>-1.4618</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6542</v>
+        <v>-1.4238</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5391</v>
+        <v>-0.5838</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5391</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.3202</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1132</v>
+        <v>-2.3018</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.459</v>
+        <v>-2.1982</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6542</v>
+        <v>-0.1035</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3645</v>
+        <v>-0.7921</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5498</v>
+        <v>-0.3286</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1853</v>
+        <v>-0.4635</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5437</v>
+        <v>1.8097</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4724</v>
+        <v>1.8097</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PARISI TRIA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9926</v>
+        <v>-1.2792</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3214</v>
+        <v>0.7634</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6712</v>
+        <v>-2.0426</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.8856</v>
+        <v>-1.8183</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4618</v>
+        <v>1.9052</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4238</v>
+        <v>-3.7234</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5838</v>
+        <v>1.7702</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7364000000000001</v>
+        <v>2.5658</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3202</v>
+        <v>-0.7956</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3018</v>
+        <v>-3.5885</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1982</v>
+        <v>-0.6607</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1035</v>
+        <v>-2.9278</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.0524</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5554</v>
+        <v>-0.2096</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1549</v>
+        <v>0.1572</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8097</v>
+        <v>0.1947</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8097</v>
+        <v>0.1947</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8692</v>
+        <v>-1.4665</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2497</v>
+        <v>1.6805</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.1189</v>
+        <v>-3.147</v>
       </c>
       <c r="G5" t="n">
         <v>-2.6229</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4924</v>
+        <v>-1.0897</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2356</v>
+        <v>-0.8048</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2569</v>
+        <v>-0.2849</v>
       </c>
       <c r="V5" t="n">
         <v>0.4607</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.4447</v>
+        <v>-3.1687</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0426</v>
+        <v>-1.3751</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.402</v>
+        <v>-1.7936</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6584</v>
+        <v>-2.5551</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.7764</v>
+        <v>0.3988</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1179</v>
+        <v>-2.9539</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1306</v>
+        <v>0.3597</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.7732</v>
+        <v>2.4003</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6425999999999999</v>
+        <v>-2.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5278</v>
+        <v>-2.9148</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0032</v>
+        <v>-2.0015</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.9133</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9478</v>
+        <v>0.3783</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4171</v>
+        <v>-0.0169</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4693</v>
+        <v>0.3953</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3673</v>
+        <v>-3.2904</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6018</v>
+        <v>-2.0006</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7655</v>
+        <v>-1.2898</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5551</v>
+        <v>-2.6584</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3988</v>
+        <v>-2.7764</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9539</v>
+        <v>0.1179</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3597</v>
+        <v>-1.1306</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4003</v>
+        <v>-1.7732</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0406</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9148</v>
+        <v>-1.5278</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0015</v>
+        <v>-1.0032</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9133</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1797</v>
+        <v>0.1021</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2436</v>
+        <v>0.4592</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4233</v>
+        <v>-0.3571</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>-0.3373</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5187</v>
+        <v>-3.6406</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8554</v>
+        <v>-2.6174</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6633</v>
+        <v>-1.0232</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0148</v>
+        <v>-3.5938</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0804</v>
+        <v>-1.2048</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9343</v>
+        <v>-2.389</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3211</v>
+        <v>-1.5972</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3211</v>
+        <v>0.4032</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.0004</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.3359</v>
+        <v>-1.9967</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4015</v>
+        <v>-1.608</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.9343</v>
+        <v>-0.3886</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1071</v>
+        <v>0.1517</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1926</v>
+        <v>-0.0283</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1799</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8268</v>
+        <v>-3.6425</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7194</v>
+        <v>-0.8951</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1074</v>
+        <v>-2.7475</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5938</v>
+        <v>-3.0148</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2048</v>
+        <v>-0.0804</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.389</v>
+        <v>-2.9343</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5972</v>
+        <v>1.3211</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4032</v>
+        <v>1.3211</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0004</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9967</v>
+        <v>-4.3359</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.608</v>
+        <v>-1.4015</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3886</v>
+        <v>-2.9343</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0345</v>
+        <v>-0.231</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1303</v>
+        <v>-0.2323</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0958</v>
+        <v>0.0014</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4225</v>
+        <v>-4.0502</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9316</v>
+        <v>-2.7276</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4909</v>
+        <v>-1.3226</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7777</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5736</v>
+        <v>-0.2012</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1122</v>
+        <v>0.2806</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6745</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1507</v>
+        <v>-6.3234</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4339</v>
+        <v>-3.6347</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7168</v>
+        <v>-2.6887</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3377</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4323</v>
+        <v>-0.6051</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1109</v>
+        <v>-0.3117</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3215</v>
+        <v>-0.2934</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.4971</v>
+        <v>-8.118399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6113</v>
+        <v>-4.3449</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8858</v>
+        <v>-3.7736</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6055</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6256</v>
+        <v>-1.247</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7481</v>
+        <v>-0.4817</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.7652</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4724</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-37.7627</v>
+        <v>-36.8276</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.6648</v>
+        <v>-15.7298</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.0978</v>
+        <v>-21.098</v>
       </c>
       <c r="G13" t="n">
-        <v>-31.52209999999999</v>
+        <v>-31.5221</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.0972</v>
+        <v>-6.097200000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-25.4248</v>
@@ -1447,7 +1447,7 @@
         <v>7.2134</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.875</v>
+        <v>-8.874999999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-29.8606</v>
@@ -1468,13 +1468,13 @@
         <v>12.8952</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.789199999999999</v>
+        <v>-3.8542</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7968</v>
+        <v>-2.8615</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9927</v>
+        <v>-0.9924999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.5246</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3763</v>
+        <v>7.2624</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5202</v>
+        <v>5.2141</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8561</v>
+        <v>2.0483</v>
       </c>
       <c r="G14" t="n">
         <v>4.4551</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>1.052</v>
+        <v>0.9381</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8106</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2414</v>
+        <v>0.4335</v>
       </c>
       <c r="V14" t="n">
         <v>1.4724</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7953</v>
+        <v>6.7256</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2035</v>
+        <v>5.0353</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5918</v>
+        <v>1.6902</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6401</v>
+        <v>5.1639</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.212</v>
+        <v>3.4926</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8521</v>
+        <v>1.6712</v>
       </c>
       <c r="J15" t="n">
-        <v>6.9435</v>
+        <v>4.9264</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3158</v>
+        <v>4.0779</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6277</v>
+        <v>0.8485</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3035</v>
+        <v>0.2374</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5278</v>
+        <v>-0.5853</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2244</v>
+        <v>0.8227</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3536</v>
+        <v>0.486</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7481</v>
+        <v>0.0171</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1018</v>
+        <v>0.469</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6516</v>
+        <v>6.6627</v>
       </c>
       <c r="E16" t="n">
-        <v>4.349</v>
+        <v>5.4075</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3026</v>
+        <v>1.2552</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9657</v>
+        <v>6.6401</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2076</v>
+        <v>-0.212</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7581</v>
+        <v>6.8521</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1315</v>
+        <v>6.9435</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1961</v>
+        <v>1.3158</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9354</v>
+        <v>5.6277</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1658</v>
+        <v>-0.3035</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9885</v>
+        <v>-1.5278</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8227</v>
+        <v>1.2244</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8247</v>
+        <v>0.221</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9353</v>
+        <v>-0.5441</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1106</v>
+        <v>0.7651</v>
       </c>
       <c r="V16" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.6312</v>
+        <v>6.4858</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1374</v>
+        <v>4.0429</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4938</v>
+        <v>2.4429</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1639</v>
+        <v>4.9657</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4926</v>
+        <v>2.2076</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6712</v>
+        <v>2.7581</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9264</v>
+        <v>5.1315</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0779</v>
+        <v>3.1961</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8485</v>
+        <v>1.9354</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2374</v>
+        <v>-0.1658</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5853</v>
+        <v>-0.9885</v>
       </c>
       <c r="O17" t="n">
         <v>0.8227</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3917</v>
+        <v>0.6589</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1191</v>
+        <v>0.6292</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2726</v>
+        <v>0.0297</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0757</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.1921</v>
+        <v>5.5238</v>
       </c>
       <c r="E18" t="n">
-        <v>4.497</v>
+        <v>3.8848</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6951</v>
+        <v>1.639</v>
       </c>
       <c r="G18" t="n">
         <v>5.4833</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>2.0938</v>
+        <v>1.4255</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6155</v>
+        <v>1.0033</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4783</v>
+        <v>0.4222</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1947</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4121</v>
+        <v>3.5958</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7082000000000001</v>
+        <v>1.1163</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7039</v>
+        <v>2.4795</v>
       </c>
       <c r="G19" t="n">
         <v>1.2233</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0544</v>
+        <v>0.238</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5611</v>
+        <v>-0.153</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6155</v>
+        <v>0.391</v>
       </c>
       <c r="V19" t="n">
         <v>0.7458</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2957</v>
+        <v>1.8013</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3085</v>
+        <v>0.1975</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6043</v>
+        <v>1.6038</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2511</v>
+        <v>1.3296</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3933</v>
+        <v>0.9268</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8579</v>
+        <v>0.4028</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2874</v>
+        <v>0.3562</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9259</v>
+        <v>0.504</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3615</v>
+        <v>-0.1479</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0363</v>
+        <v>0.9734</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5327</v>
+        <v>0.4228</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4964</v>
+        <v>0.5507</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5604</v>
+        <v>-0.2381</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3798</v>
+        <v>-0.1586</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1806</v>
+        <v>-0.0794</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.532</v>
+        <v>-1.4724</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2934</v>
+        <v>1.7763</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0825</v>
+        <v>-0.1845</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3759</v>
+        <v>1.9609</v>
       </c>
       <c r="G21" t="n">
         <v>1.141</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>0.22</v>
+        <v>0.7029</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1304</v>
+        <v>0.0284</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0895</v>
+        <v>0.6744</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7266</v>
+        <v>1.0432</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5167</v>
+        <v>-0.3085</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2433</v>
+        <v>1.3518</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3296</v>
+        <v>2.2511</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9268</v>
+        <v>0.3933</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4028</v>
+        <v>1.8579</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3562</v>
+        <v>2.2874</v>
       </c>
       <c r="K22" t="n">
-        <v>0.504</v>
+        <v>1.9259</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1479</v>
+        <v>0.3615</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9734</v>
+        <v>-0.0363</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4228</v>
+        <v>-1.5327</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5507</v>
+        <v>1.4964</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3128</v>
+        <v>1.3079</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8728</v>
+        <v>0.3798</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4399</v>
+        <v>0.9281</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4724</v>
+        <v>-0.532</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4724</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2675</v>
+        <v>0.0165</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0273</v>
+        <v>-0.8232</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7598</v>
+        <v>0.8398</v>
       </c>
       <c r="G23" t="n">
         <v>1.2311</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5419</v>
+        <v>-0.2579</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1439</v>
+        <v>0.2238</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1469</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3442</v>
+        <v>-2.4505</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3824</v>
+        <v>-2.4844</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0381</v>
+        <v>0.0339</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3621</v>
@@ -2326,13 +2326,13 @@
         <v>0.7935</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0935</v>
+        <v>-0.0127</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1303</v>
+        <v>-0.2323</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2238</v>
+        <v>0.2196</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8692</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>37.7626</v>
+        <v>38.4429</v>
       </c>
       <c r="E25" t="n">
-        <v>21.0979</v>
+        <v>21.0978</v>
       </c>
       <c r="F25" t="n">
-        <v>16.6647</v>
+        <v>17.3453</v>
       </c>
       <c r="G25" t="n">
         <v>31.5221</v>
       </c>
       <c r="H25" t="n">
-        <v>6.097300000000001</v>
+        <v>6.0973</v>
       </c>
       <c r="I25" t="n">
         <v>25.4248</v>
       </c>
       <c r="J25" t="n">
-        <v>29.8605</v>
+        <v>29.86049999999999</v>
       </c>
       <c r="K25" t="n">
         <v>13.3107</v>
@@ -2389,10 +2389,10 @@
         <v>1.6615</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.213500000000001</v>
+        <v>-7.213500000000002</v>
       </c>
       <c r="O25" t="n">
-        <v>8.875100000000002</v>
+        <v>8.8751</v>
       </c>
       <c r="P25" t="n">
         <v>2.9758</v>
@@ -2404,13 +2404,13 @@
         <v>15.8707</v>
       </c>
       <c r="S25" t="n">
-        <v>4.789399999999999</v>
+        <v>5.4696</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9925999999999998</v>
+        <v>0.9925999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>3.7969</v>
+        <v>4.476999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5246</v>
